--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Trabalho\rs\redisexcel\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91200812-EF9C-4919-A000-6D118A15F05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1FD7105-75C2-4302-A59D-83DC5EB54AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{2FD05B7C-2628-44E8-97E9-EE31C04382F8}"/>
+    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{B75BC407-9E05-497C-9A85-4480C64E9676}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -568,7 +568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF80DD27-C2DE-44B8-AD8E-24CBF73AF86A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D7C84E4-562D-44D2-8FD0-F3F4BDAB2D08}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -737,7 +737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B779AD-F89F-45F7-B4F4-7D963C7E7FBE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{670B3D57-A4DF-4E4E-8897-19D727618726}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -862,7 +862,7 @@
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
-        <v>100</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Trabalho\rs\redisexcel\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1FD7105-75C2-4302-A59D-83DC5EB54AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D21BDBF1-E01C-4D63-B10D-7D4B6F020492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{B75BC407-9E05-497C-9A85-4480C64E9676}"/>
+    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{EBB1DE32-8B08-455A-90D2-CBB6CF60AFAB}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -568,7 +568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D7C84E4-562D-44D2-8FD0-F3F4BDAB2D08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{648815EF-15FD-4223-A28D-F642C3019C5B}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -737,7 +737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{670B3D57-A4DF-4E4E-8897-19D727618726}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91F829D1-B7A4-4FCC-8120-0BFAF2059B03}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Trabalho\rs\redisexcel\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D21BDBF1-E01C-4D63-B10D-7D4B6F020492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AF803E0-5C49-42B9-9924-E0F868EDFFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{EBB1DE32-8B08-455A-90D2-CBB6CF60AFAB}"/>
+    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{6153C744-F487-4E41-AB5B-2473C7925BE8}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -568,7 +568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{648815EF-15FD-4223-A28D-F642C3019C5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33742EAC-9AC9-4E2A-A218-0C9C4BE199D2}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -737,7 +737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91F829D1-B7A4-4FCC-8120-0BFAF2059B03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2270D1C5-1EC3-4EB8-8294-80B6A0AB7154}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Trabalho\rs\redisexcel\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AF803E0-5C49-42B9-9924-E0F868EDFFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29AE7CFA-8733-4D89-9EEF-2BAEC5A19486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{6153C744-F487-4E41-AB5B-2473C7925BE8}"/>
+    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{F7E7A266-0222-40F0-95E5-98E45C134E4A}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -568,7 +568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33742EAC-9AC9-4E2A-A218-0C9C4BE199D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5A6E3E4-16F2-4F3B-BF71-D88438E08679}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -737,7 +737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2270D1C5-1EC3-4EB8-8294-80B6A0AB7154}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADDA315-F006-456F-BD92-186F0490E787}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Trabalho\rs\redisexcel\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29AE7CFA-8733-4D89-9EEF-2BAEC5A19486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AB7176B-244D-4F21-8680-880582F4DB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{F7E7A266-0222-40F0-95E5-98E45C134E4A}"/>
+    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{0188E7DD-49A3-410D-ABB2-C6BA0600603B}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -568,7 +568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5A6E3E4-16F2-4F3B-BF71-D88438E08679}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E534DB3-4378-4335-A6F9-524FD54A5A47}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -737,7 +737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADDA315-F006-456F-BD92-186F0490E787}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E32D44C4-38AB-41F3-8D41-0941621B884B}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Trabalho\rs\redisexcel\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AB7176B-244D-4F21-8680-880582F4DB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F837E30E-E852-4F1E-9DAF-FA514E05042E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{0188E7DD-49A3-410D-ABB2-C6BA0600603B}"/>
+    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{FF395B52-4190-4BF1-AE53-299997F12B4F}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -106,6 +106,15 @@
   </si>
   <si>
     <t>ConnectionCount</t>
+  </si>
+  <si>
+    <t>ExistsMultiples</t>
+  </si>
+  <si>
+    <t>TTLMultiples</t>
+  </si>
+  <si>
+    <t>HashGetFieldMultipleKeys</t>
   </si>
   <si>
     <t>RedisExcel RTD tests (host localhost:6379)</t>
@@ -568,8 +577,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E534DB3-4378-4335-A6F9-524FD54A5A47}">
-  <dimension ref="A1:G14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{927A6C7C-9621-4CA0-8B6B-51495E5D03BF}">
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -729,6 +738,42 @@
       <c r="B14">
         <f ca="1">_xll.RedisUDFConnectionCount()</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="str">
+        <f ca="1">INDEX(_xll.RedisUDFExistsMultiples({"test.redisexcel.key","test.redisexcel.missing"},"localhost:6379"),1,2)</f>
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="str">
+        <f ca="1">INDEX(_xll.RedisUDFTTLMultiples({"test.redisexcel.key"},"localhost:6379"),1,2)</f>
+        <v>-1</v>
+      </c>
+      <c r="C16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="str">
+        <f ca="1">INDEX(_xll.RedisUDFHashGetFieldMultipleKeys({"test.redisexcel.hash","test.redisexcel.hash"},"campo1","localhost:6379"),2,2)</f>
+        <v>valor1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -737,13 +782,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E32D44C4-38AB-41F3-8D41-0941621B884B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F3DEB0-CC94-4B2A-A945-A35DD515B1E7}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -759,7 +804,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B4" t="str">
         <f>RTD("redisrtd",,"GET","test.redisexcel.key","localhost:6379")</f>
@@ -771,7 +816,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B5" t="str">
         <f>RTD("redisrtd",,"HGET","test.redisexcel.hash","campo1","localhost:6379")</f>
@@ -783,19 +828,19 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B6" t="str">
         <f>RTD("redisrtd",,"HGETALL","test.redisexcel.hash","localhost:6379")</f>
         <v>{"campo1":"valor1"}</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B7" t="str">
         <f>RTD("redisrtd",,"SUB","test.redisexcel.rtd","localhost:6379")</f>
@@ -804,7 +849,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B8" t="str">
         <f>RTD("redisrtd",,"PSUB","test.redisexcel.rtd*","localhost:6379")</f>
@@ -822,7 +867,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B10">
         <f ca="1">_xll.RedisRTDTopicCount()</f>
@@ -831,7 +876,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B11">
         <f ca="1">_xll.RedisRTDSubscriptionCount()</f>
@@ -840,7 +885,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B12">
         <f ca="1">_xll.RedisRTDChannelCount()</f>
@@ -849,7 +894,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">_xll.RedisRTDDefaultHost()</f>
@@ -858,7 +903,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
@@ -867,7 +912,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B15">
         <f ca="1">_xll.RedisRTDRedisUpdateInterval()</f>
@@ -876,7 +921,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B16" t="b">
         <f ca="1">_xll.RedisRTDRealTimeUpdates()</f>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Trabalho\rs\redisexcel\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F837E30E-E852-4F1E-9DAF-FA514E05042E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74C505F9-D9EA-4227-B08C-1CD3FC5ADA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{FF395B52-4190-4BF1-AE53-299997F12B4F}"/>
+    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{7DCCFD11-588E-476C-99AA-9DD73AD6168A}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -577,7 +577,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{927A6C7C-9621-4CA0-8B6B-51495E5D03BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6404B3-2E51-47D8-8DC4-93DF1B0E6145}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -782,7 +782,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F3DEB0-CC94-4B2A-A945-A35DD515B1E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E2A475C-EA32-44E3-87B8-91352767C45F}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Trabalho\rs\redisexcel\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74C505F9-D9EA-4227-B08C-1CD3FC5ADA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0C87F29-FA8B-4BBF-B99D-EA01A839BC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="-28770" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{7DCCFD11-588E-476C-99AA-9DD73AD6168A}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{0A22C42D-A324-47FF-AA6E-F64AF4F388CD}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="48">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -115,6 +115,33 @@
   </si>
   <si>
     <t>HashGetFieldMultipleKeys</t>
+  </si>
+  <si>
+    <t>SetEx</t>
+  </si>
+  <si>
+    <t>Del</t>
+  </si>
+  <si>
+    <t>Incr</t>
+  </si>
+  <si>
+    <t>ListPushRight</t>
+  </si>
+  <si>
+    <t>ListRange</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>SetAdd</t>
+  </si>
+  <si>
+    <t>SetMembers</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
   <si>
     <t>RedisExcel RTD tests (host localhost:6379)</t>
@@ -577,8 +604,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6404B3-2E51-47D8-8DC4-93DF1B0E6145}">
-  <dimension ref="A1:G17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F9548D4-259F-4C6C-ABE2-D60F74645A77}">
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -774,6 +801,93 @@
       </c>
       <c r="C17" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="str">
+        <f ca="1">_xll.RedisUDFSetEx("test.redisexcel.tmp","x","100","localhost:6379")</f>
+        <v>OK</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
+        <v>97.978999999999999</v>
+      </c>
+      <c r="C19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20">
+        <f ca="1">_xll.RedisUDFDel("test.redisexcel.neverexists","localhost:6379")</f>
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21">
+        <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22">
+        <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="str">
+        <f ca="1">INDEX(_xll.RedisUDFListRange("test.redisexcel.list",0,-1,"localhost:6379"),1,1)</f>
+        <v>a</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24">
+        <f ca="1">_xll.RedisUDFSetAdd("test.redisexcel.set","x","localhost:6379")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="str">
+        <f ca="1">INDEX(_xll.RedisUDFSetMembers("test.redisexcel.set","localhost:6379"),1,1)</f>
+        <v>x</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -782,13 +896,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E2A475C-EA32-44E3-87B8-91352767C45F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3432E014-9B3A-4CDC-AE5D-132CD7118DF5}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -804,7 +918,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B4" t="str">
         <f>RTD("redisrtd",,"GET","test.redisexcel.key","localhost:6379")</f>
@@ -816,7 +930,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B5" t="str">
         <f>RTD("redisrtd",,"HGET","test.redisexcel.hash","campo1","localhost:6379")</f>
@@ -828,19 +942,19 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B6" t="str">
         <f>RTD("redisrtd",,"HGETALL","test.redisexcel.hash","localhost:6379")</f>
         <v>{"campo1":"valor1"}</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B7" t="str">
         <f>RTD("redisrtd",,"SUB","test.redisexcel.rtd","localhost:6379")</f>
@@ -849,7 +963,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B8" t="str">
         <f>RTD("redisrtd",,"PSUB","test.redisexcel.rtd*","localhost:6379")</f>
@@ -867,7 +981,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B10">
         <f ca="1">_xll.RedisRTDTopicCount()</f>
@@ -876,7 +990,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B11">
         <f ca="1">_xll.RedisRTDSubscriptionCount()</f>
@@ -885,7 +999,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B12">
         <f ca="1">_xll.RedisRTDChannelCount()</f>
@@ -894,7 +1008,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">_xll.RedisRTDDefaultHost()</f>
@@ -903,7 +1017,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
@@ -912,7 +1026,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B15">
         <f ca="1">_xll.RedisRTDRedisUpdateInterval()</f>
@@ -921,7 +1035,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B16" t="b">
         <f ca="1">_xll.RedisRTDRealTimeUpdates()</f>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Trabalho\rs\redisexcel\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0C87F29-FA8B-4BBF-B99D-EA01A839BC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{406CD45B-5EAF-4E00-974C-3FD9C59A339F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{0A22C42D-A324-47FF-AA6E-F64AF4F388CD}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{4C560AC9-5762-4CD1-9607-A920D47AF5C5}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="50">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t>x</t>
+  </si>
+  <si>
+    <t>Set locale</t>
+  </si>
+  <si>
+    <t>Get locale</t>
   </si>
   <si>
     <t>RedisExcel RTD tests (host localhost:6379)</t>
@@ -604,24 +610,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F9548D4-259F-4C6C-ABE2-D60F74645A77}">
-  <dimension ref="A1:G25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C308DF55-55A5-42A2-85D4-E204028C076A}">
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2">
+        <v>67000.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -638,7 +647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -650,7 +659,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -662,7 +671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -674,7 +683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -686,7 +695,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -698,7 +707,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -710,7 +719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -722,7 +731,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -734,7 +743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -746,7 +755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -758,7 +767,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -767,7 +776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -779,7 +788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -821,7 +830,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>97.978999999999999</v>
+        <v>98.003999999999991</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -845,7 +854,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -854,7 +863,7 @@
       </c>
       <c r="B22">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -888,6 +897,30 @@
       </c>
       <c r="C25" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="str">
+        <f ca="1">_xll.RedisUDFSet("test.redisexcel.locale",$H$2,"localhost:6379")</f>
+        <v>OK</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="str">
+        <f ca="1">_xll.RedisUDFGet("test.redisexcel.locale","localhost:6379")</f>
+        <v>67000.5</v>
+      </c>
+      <c r="C27">
+        <v>67000.5</v>
       </c>
     </row>
   </sheetData>
@@ -896,13 +929,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3432E014-9B3A-4CDC-AE5D-132CD7118DF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC63899-ACE3-40BB-BEF0-DB0E485FFEDC}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,7 +951,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" t="str">
         <f>RTD("redisrtd",,"GET","test.redisexcel.key","localhost:6379")</f>
@@ -930,7 +963,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" t="str">
         <f>RTD("redisrtd",,"HGET","test.redisexcel.hash","campo1","localhost:6379")</f>
@@ -942,19 +975,19 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6" t="str">
         <f>RTD("redisrtd",,"HGETALL","test.redisexcel.hash","localhost:6379")</f>
         <v>{"campo1":"valor1"}</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B7" t="str">
         <f>RTD("redisrtd",,"SUB","test.redisexcel.rtd","localhost:6379")</f>
@@ -963,7 +996,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" t="str">
         <f>RTD("redisrtd",,"PSUB","test.redisexcel.rtd*","localhost:6379")</f>
@@ -981,7 +1014,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <f ca="1">_xll.RedisRTDTopicCount()</f>
@@ -990,7 +1023,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <f ca="1">_xll.RedisRTDSubscriptionCount()</f>
@@ -999,7 +1032,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <f ca="1">_xll.RedisRTDChannelCount()</f>
@@ -1008,7 +1041,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">_xll.RedisRTDDefaultHost()</f>
@@ -1017,7 +1050,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
@@ -1026,7 +1059,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <f ca="1">_xll.RedisRTDRedisUpdateInterval()</f>
@@ -1035,7 +1068,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16" t="b">
         <f ca="1">_xll.RedisRTDRealTimeUpdates()</f>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Trabalho\rs\redisexcel\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{406CD45B-5EAF-4E00-974C-3FD9C59A339F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19215FAA-D6BE-481C-BD92-0CF73A07DFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{4C560AC9-5762-4CD1-9607-A920D47AF5C5}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{64B0A41C-6621-4A41-B75C-58FBECAC393A}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="61">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -148,6 +148,39 @@
   </si>
   <si>
     <t>Get locale</t>
+  </si>
+  <si>
+    <t>Set numeric key</t>
+  </si>
+  <si>
+    <t>Get numeric key</t>
+  </si>
+  <si>
+    <t>dec-key</t>
+  </si>
+  <si>
+    <t>HashDel missing</t>
+  </si>
+  <si>
+    <t>SetRemove missing</t>
+  </si>
+  <si>
+    <t>Type missing</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>Type string</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Type list</t>
+  </si>
+  <si>
+    <t>list</t>
   </si>
   <si>
     <t>RedisExcel RTD tests (host localhost:6379)</t>
@@ -610,8 +643,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C308DF55-55A5-42A2-85D4-E204028C076A}">
-  <dimension ref="A1:H27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89E4B8E8-3DA8-4DEC-937A-A568F1F12DF4}">
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -830,7 +863,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.003999999999991</v>
+        <v>97.998999999999995</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -854,7 +887,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>69</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,7 +896,7 @@
       </c>
       <c r="B22">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>66</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -921,6 +954,90 @@
       </c>
       <c r="C27">
         <v>67000.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="str">
+        <f ca="1">_xll.RedisUDFSet($H$2,"dec-key","localhost:6379")</f>
+        <v>OK</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" t="str">
+        <f ca="1">_xll.RedisUDFGet($H$2,"localhost:6379")</f>
+        <v>dec-key</v>
+      </c>
+      <c r="C29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30">
+        <f ca="1">_xll.RedisUDFHashDel("test.redisexcel.hash","missing","localhost:6379")</f>
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31">
+        <f ca="1">_xll.RedisUDFSetRemove("test.redisexcel.set","missing","localhost:6379")</f>
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" t="str">
+        <f ca="1">_xll.RedisUDFType("test.redisexcel.missingkey","localhost:6379")</f>
+        <v>none</v>
+      </c>
+      <c r="C32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="str">
+        <f ca="1">_xll.RedisUDFType("test.redisexcel.key","localhost:6379")</f>
+        <v>string</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" t="str">
+        <f ca="1">_xll.RedisUDFType("test.redisexcel.list","localhost:6379")</f>
+        <v>list</v>
+      </c>
+      <c r="C34" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -929,13 +1046,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC63899-ACE3-40BB-BEF0-DB0E485FFEDC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBFCE4A-F2DE-40D8-971D-75E01D30D6C7}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,7 +1068,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B4" t="str">
         <f>RTD("redisrtd",,"GET","test.redisexcel.key","localhost:6379")</f>
@@ -963,7 +1080,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B5" t="str">
         <f>RTD("redisrtd",,"HGET","test.redisexcel.hash","campo1","localhost:6379")</f>
@@ -975,19 +1092,19 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B6" t="str">
         <f>RTD("redisrtd",,"HGETALL","test.redisexcel.hash","localhost:6379")</f>
         <v>{"campo1":"valor1"}</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B7" t="str">
         <f>RTD("redisrtd",,"SUB","test.redisexcel.rtd","localhost:6379")</f>
@@ -996,7 +1113,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B8" t="str">
         <f>RTD("redisrtd",,"PSUB","test.redisexcel.rtd*","localhost:6379")</f>
@@ -1014,7 +1131,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <f ca="1">_xll.RedisRTDTopicCount()</f>
@@ -1023,25 +1140,25 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <f ca="1">_xll.RedisRTDSubscriptionCount()</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B12">
         <f ca="1">_xll.RedisRTDChannelCount()</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">_xll.RedisRTDDefaultHost()</f>
@@ -1050,7 +1167,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
@@ -1059,7 +1176,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B15">
         <f ca="1">_xll.RedisRTDRedisUpdateInterval()</f>
@@ -1068,7 +1185,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B16" t="b">
         <f ca="1">_xll.RedisRTDRealTimeUpdates()</f>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Trabalho\rs\redisexcel\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19215FAA-D6BE-481C-BD92-0CF73A07DFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CE06222-47C0-4F6B-A7A2-625309AFB61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{64B0A41C-6621-4A41-B75C-58FBECAC393A}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{93CF80EF-2C99-493C-9AD3-887C85167635}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -181,6 +181,18 @@
   </si>
   <si>
     <t>list</t>
+  </si>
+  <si>
+    <t>ListPopRight empty</t>
+  </si>
+  <si>
+    <t>empty</t>
+  </si>
+  <si>
+    <t>ListPopLeft empty</t>
+  </si>
+  <si>
+    <t>Rename missing</t>
   </si>
   <si>
     <t>RedisExcel RTD tests (host localhost:6379)</t>
@@ -643,8 +655,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89E4B8E8-3DA8-4DEC-937A-A568F1F12DF4}">
-  <dimension ref="A1:H34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2551F65E-DCCD-4250-8F86-FF5E8C77C661}">
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -863,7 +875,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>97.998999999999995</v>
+        <v>98.32</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -887,7 +899,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,7 +908,7 @@
       </c>
       <c r="B22">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1038,6 +1050,39 @@
       </c>
       <c r="C34" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" t="str">
+        <f ca="1">IF(_xll.RedisUDFListPopRight("test.redisexcel.emptylist","localhost:6379")="","empty","not empty")</f>
+        <v>empty</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" t="str">
+        <f ca="1">IF(_xll.RedisUDFListPopLeft("test.redisexcel.emptylist","localhost:6379")="","empty","not empty")</f>
+        <v>empty</v>
+      </c>
+      <c r="C36" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" t="str">
+        <f ca="1">_xll.RedisUDFRename("test.redisexcel.missingrename","test.redisexcel.renamed","localhost:6379")</f>
+        <v>Error: ERR no such key</v>
       </c>
     </row>
   </sheetData>
@@ -1046,13 +1091,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EBFCE4A-F2DE-40D8-971D-75E01D30D6C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D958298-D33C-40D7-89D0-55D32C3EFBEF}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1068,7 +1113,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B4" t="str">
         <f>RTD("redisrtd",,"GET","test.redisexcel.key","localhost:6379")</f>
@@ -1080,7 +1125,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B5" t="str">
         <f>RTD("redisrtd",,"HGET","test.redisexcel.hash","campo1","localhost:6379")</f>
@@ -1092,19 +1137,19 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B6" t="str">
         <f>RTD("redisrtd",,"HGETALL","test.redisexcel.hash","localhost:6379")</f>
         <v>{"campo1":"valor1"}</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B7" t="str">
         <f>RTD("redisrtd",,"SUB","test.redisexcel.rtd","localhost:6379")</f>
@@ -1113,7 +1158,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B8" t="str">
         <f>RTD("redisrtd",,"PSUB","test.redisexcel.rtd*","localhost:6379")</f>
@@ -1131,7 +1176,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B10">
         <f ca="1">_xll.RedisRTDTopicCount()</f>
@@ -1140,7 +1185,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B11">
         <f ca="1">_xll.RedisRTDSubscriptionCount()</f>
@@ -1149,7 +1194,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <f ca="1">_xll.RedisRTDChannelCount()</f>
@@ -1158,7 +1203,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">_xll.RedisRTDDefaultHost()</f>
@@ -1167,7 +1212,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
@@ -1176,7 +1221,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B15">
         <f ca="1">_xll.RedisRTDRedisUpdateInterval()</f>
@@ -1185,7 +1230,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B16" t="b">
         <f ca="1">_xll.RedisRTDRealTimeUpdates()</f>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CE06222-47C0-4F6B-A7A2-625309AFB61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48488D42-19E9-4FD1-9A37-4194D166EAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{93CF80EF-2C99-493C-9AD3-887C85167635}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{176280A2-0CD6-45E2-81CA-AA2AF9E0DF54}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -655,7 +655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2551F65E-DCCD-4250-8F86-FF5E8C77C661}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6836355F-BD05-45D5-9F72-EE24E20C1A53}">
   <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -875,7 +875,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.32</v>
+        <v>98.323999999999998</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1091,7 +1091,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D958298-D33C-40D7-89D0-55D32C3EFBEF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03C9E21-11FB-433D-892B-FEE90B9E52AA}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48488D42-19E9-4FD1-9A37-4194D166EAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C51BE2DA-63AC-4F85-A423-CCD3816A773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{176280A2-0CD6-45E2-81CA-AA2AF9E0DF54}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{51BC989B-C48B-4C10-A711-11436BE17E72}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -655,7 +655,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6836355F-BD05-45D5-9F72-EE24E20C1A53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3653A3-8207-48BB-88F3-8EBA412FB31D}">
   <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -875,7 +875,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.323999999999998</v>
+        <v>97.983999999999995</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1091,7 +1091,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03C9E21-11FB-433D-892B-FEE90B9E52AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D72A32-1CB0-40F4-91C6-6B1105041575}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -4,13 +4,11 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\AppData\Local\Temp\"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C51BE2DA-63AC-4F85-A423-CCD3816A773D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6021AD0C-3095-48A8-BA17-B5813DB399E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{51BC989B-C48B-4C10-A711-11436BE17E72}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{74C0D61D-78F1-4ABE-9265-B10751B5643D}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -655,7 +653,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE3653A3-8207-48BB-88F3-8EBA412FB31D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E02B1D6-AE72-45B6-873D-43D0E8D1ED81}">
   <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -875,7 +873,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>97.983999999999995</v>
+        <v>98</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1091,7 +1089,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D72A32-1CB0-40F4-91C6-6B1105041575}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FA3CE4D-1117-443C-B0CB-C07FCCD8CB51}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6021AD0C-3095-48A8-BA17-B5813DB399E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{675F28A0-D04B-4C84-A89C-029E764D315D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{74C0D61D-78F1-4ABE-9265-B10751B5643D}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{6A1CB3C3-CA8A-456F-B006-CED773E5E31C}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -233,6 +233,15 @@
   </si>
   <si>
     <t>RealTimeUpdates</t>
+  </si>
+  <si>
+    <t>GET missing key</t>
+  </si>
+  <si>
+    <t>GET whitespace key</t>
+  </si>
+  <si>
+    <t>ws_key_value</t>
   </si>
 </sst>
 </file>
@@ -309,6 +318,12 @@
         <tr r="B5" s="2"/>
       </tp>
       <tp t="s">
+        <v>#ERROR: ConnectData: GET requires a key as the second argument</v>
+        <stp/>
+        <stp>GET</stp>
+        <tr r="B20" s="2"/>
+      </tp>
+      <tp t="s">
         <v>ALTA</v>
         <stp/>
         <stp>PSUB</stp>
@@ -331,6 +346,14 @@
         <stp>test.redisexcel.key</stp>
         <stp>localhost:6379</stp>
         <tr r="B4" s="2"/>
+      </tp>
+      <tp t="s">
+        <v>ws_key_value</v>
+        <stp/>
+        <stp>GET</stp>
+        <stp xml:space="preserve"> </stp>
+        <stp>localhost:6379</stp>
+        <tr r="B21" s="2"/>
       </tp>
     </main>
   </volType>
@@ -653,7 +676,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E02B1D6-AE72-45B6-873D-43D0E8D1ED81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492AC1C8-B5E6-4FF1-B83F-197889D4D90B}">
   <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -873,7 +896,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98</v>
+        <v>98.003</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -897,7 +920,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -906,7 +929,7 @@
       </c>
       <c r="B22">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1089,8 +1112,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FA3CE4D-1117-443C-B0CB-C07FCCD8CB51}">
-  <dimension ref="A1:C16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ECDE5F6-AC68-49B5-AE01-DE8FC87A9788}">
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1178,7 +1201,7 @@
       </c>
       <c r="B10">
         <f ca="1">_xll.RedisRTDTopicCount()</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1233,6 +1256,27 @@
       <c r="B16" t="b">
         <f ca="1">_xll.RedisRTDRealTimeUpdates()</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" t="str">
+        <f>RTD("redisrtd",,"GET")</f>
+        <v>#ERROR: ConnectData: GET requires a key as the second argument</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" t="str">
+        <f>RTD("redisrtd",,"GET"," ","localhost:6379")</f>
+        <v>ws_key_value</v>
+      </c>
+      <c r="C21" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{675F28A0-D04B-4C84-A89C-029E764D315D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9CE0ACB-A6E5-4796-BF95-67E5116CCAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{6A1CB3C3-CA8A-456F-B006-CED773E5E31C}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{F3DA4C6D-5892-4F22-86B7-29D9DD48B7F1}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="73">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -191,6 +191,21 @@
   </si>
   <si>
     <t>Rename missing</t>
+  </si>
+  <si>
+    <t>Get range arg</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>GetMultiple no keys</t>
+  </si>
+  <si>
+    <t>ExistsMultiples 2x2</t>
+  </si>
+  <si>
+    <t>Keys blank pattern</t>
   </si>
   <si>
     <t>RedisExcel RTD tests (host localhost:6379)</t>
@@ -676,8 +691,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492AC1C8-B5E6-4FF1-B83F-197889D4D90B}">
-  <dimension ref="A1:H37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3399171C-3D63-4FC3-8023-35777CABE3F6}">
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -839,7 +854,7 @@
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisUDFConnectionCount()</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -896,7 +911,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.003</v>
+        <v>97.983999999999995</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -920,7 +935,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,7 +944,7 @@
       </c>
       <c r="B22">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1104,6 +1119,45 @@
       <c r="B37" t="str">
         <f ca="1">_xll.RedisUDFRename("test.redisexcel.missingrename","test.redisexcel.renamed","localhost:6379")</f>
         <v>Error: ERR no such key</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" t="str">
+        <f ca="1">IF(ISNUMBER(SEARCH("Error",_xll.RedisUDFGet($F$2:$G$2))),"error","no error")</f>
+        <v>error</v>
+      </c>
+      <c r="C38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" t="str">
+        <f ca="1">_xll.RedisUDFGetMultiple("",FALSE)</f>
+        <v>Error: No valid key</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" t="str">
+        <f ca="1">INDEX(_xll.RedisUDFExistsMultiples({"test.redisexcel.key","test.redisexcel.missing1";"test.redisexcel.missing2","test.redisexcel.missing3"},"localhost:6379"),2,1)</f>
+        <v>test.redisexcel.missing1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" t="str">
+        <f ca="1">_xll.RedisUDFKeys($J$3)</f>
+        <v>Error: a key pattern is required; use "*" to match all keys</v>
       </c>
     </row>
   </sheetData>
@@ -1112,13 +1166,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ECDE5F6-AC68-49B5-AE01-DE8FC87A9788}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2E2530D-5978-491F-B363-C1809F650724}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1134,7 +1188,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B4" t="str">
         <f>RTD("redisrtd",,"GET","test.redisexcel.key","localhost:6379")</f>
@@ -1146,7 +1200,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B5" t="str">
         <f>RTD("redisrtd",,"HGET","test.redisexcel.hash","campo1","localhost:6379")</f>
@@ -1158,19 +1212,19 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B6" t="str">
         <f>RTD("redisrtd",,"HGETALL","test.redisexcel.hash","localhost:6379")</f>
         <v>{"campo1":"valor1"}</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B7" t="str">
         <f>RTD("redisrtd",,"SUB","test.redisexcel.rtd","localhost:6379")</f>
@@ -1179,7 +1233,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B8" t="str">
         <f>RTD("redisrtd",,"PSUB","test.redisexcel.rtd*","localhost:6379")</f>
@@ -1197,7 +1251,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B10">
         <f ca="1">_xll.RedisRTDTopicCount()</f>
@@ -1206,7 +1260,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B11">
         <f ca="1">_xll.RedisRTDSubscriptionCount()</f>
@@ -1215,7 +1269,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B12">
         <f ca="1">_xll.RedisRTDChannelCount()</f>
@@ -1224,7 +1278,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">_xll.RedisRTDDefaultHost()</f>
@@ -1233,7 +1287,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
@@ -1242,7 +1296,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B15">
         <f ca="1">_xll.RedisRTDRedisUpdateInterval()</f>
@@ -1251,7 +1305,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B16" t="b">
         <f ca="1">_xll.RedisRTDRealTimeUpdates()</f>
@@ -1260,7 +1314,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B20" t="str">
         <f>RTD("redisrtd",,"GET")</f>
@@ -1269,14 +1323,14 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B21" t="str">
         <f>RTD("redisrtd",,"GET"," ","localhost:6379")</f>
         <v>ws_key_value</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9CE0ACB-A6E5-4796-BF95-67E5116CCAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4939C1D-B5E5-433A-B26A-A68AEE3AC6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{F3DA4C6D-5892-4F22-86B7-29D9DD48B7F1}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{9B7465AA-6FDB-4F3D-988B-81C7F7636BDD}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="74">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -206,6 +206,9 @@
   </si>
   <si>
     <t>Keys blank pattern</t>
+  </si>
+  <si>
+    <t>GetMultiple 2x2</t>
   </si>
   <si>
     <t>RedisExcel RTD tests (host localhost:6379)</t>
@@ -691,8 +694,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3399171C-3D63-4FC3-8023-35777CABE3F6}">
-  <dimension ref="A1:H41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260B408D-23B5-436D-B088-28C0A70F2DB5}">
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -854,7 +857,7 @@
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisUDFConnectionCount()</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -911,7 +914,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>97.983999999999995</v>
+        <v>97.991</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -935,7 +938,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -944,7 +947,7 @@
       </c>
       <c r="B22">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1158,6 +1161,15 @@
       <c r="B41" t="str">
         <f ca="1">_xll.RedisUDFKeys($J$3)</f>
         <v>Error: a key pattern is required; use "*" to match all keys</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" t="str">
+        <f ca="1">INDEX(_xll.RedisUDFGetMultiple($F$2:$G$3,TRUE,"localhost:6379"),2,1)</f>
+        <v>linha1</v>
       </c>
     </row>
   </sheetData>
@@ -1166,13 +1178,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2E2530D-5978-491F-B363-C1809F650724}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{570C164C-BACA-45EE-A434-9925DD3C362F}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1188,7 +1200,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B4" t="str">
         <f>RTD("redisrtd",,"GET","test.redisexcel.key","localhost:6379")</f>
@@ -1200,7 +1212,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" t="str">
         <f>RTD("redisrtd",,"HGET","test.redisexcel.hash","campo1","localhost:6379")</f>
@@ -1212,19 +1224,19 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B6" t="str">
         <f>RTD("redisrtd",,"HGETALL","test.redisexcel.hash","localhost:6379")</f>
         <v>{"campo1":"valor1"}</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B7" t="str">
         <f>RTD("redisrtd",,"SUB","test.redisexcel.rtd","localhost:6379")</f>
@@ -1233,7 +1245,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" t="str">
         <f>RTD("redisrtd",,"PSUB","test.redisexcel.rtd*","localhost:6379")</f>
@@ -1251,7 +1263,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10">
         <f ca="1">_xll.RedisRTDTopicCount()</f>
@@ -1260,7 +1272,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B11">
         <f ca="1">_xll.RedisRTDSubscriptionCount()</f>
@@ -1269,7 +1281,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B12">
         <f ca="1">_xll.RedisRTDChannelCount()</f>
@@ -1278,7 +1290,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">_xll.RedisRTDDefaultHost()</f>
@@ -1287,7 +1299,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
@@ -1296,7 +1308,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15">
         <f ca="1">_xll.RedisRTDRedisUpdateInterval()</f>
@@ -1305,7 +1317,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B16" t="b">
         <f ca="1">_xll.RedisRTDRealTimeUpdates()</f>
@@ -1314,7 +1326,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" t="str">
         <f>RTD("redisrtd",,"GET")</f>
@@ -1323,14 +1335,14 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" t="str">
         <f>RTD("redisrtd",,"GET"," ","localhost:6379")</f>
         <v>ws_key_value</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4939C1D-B5E5-433A-B26A-A68AEE3AC6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{718E9C97-F3BD-48EA-9D2C-DBF4AC74E041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{9B7465AA-6FDB-4F3D-988B-81C7F7636BDD}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{314ABDF6-4D98-4849-A9C5-078FB1684D1B}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="75">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>GetMultiple 2x2</t>
+  </si>
+  <si>
+    <t>SetKV mismatched</t>
   </si>
   <si>
     <t>RedisExcel RTD tests (host localhost:6379)</t>
@@ -694,8 +697,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260B408D-23B5-436D-B088-28C0A70F2DB5}">
-  <dimension ref="A1:H42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9872A662-9EB2-41B4-B0E1-22D68B3BC39D}">
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -914,7 +917,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>97.991</v>
+        <v>98.015000000000001</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -938,7 +941,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -947,7 +950,7 @@
       </c>
       <c r="B22">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1170,6 +1173,15 @@
       <c r="B42" t="str">
         <f ca="1">INDEX(_xll.RedisUDFGetMultiple($F$2:$G$3,TRUE,"localhost:6379"),2,1)</f>
         <v>linha1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" t="str">
+        <f ca="1">_xll.RedisUDFSetKV($F$2:$G$2,$F$3)</f>
+        <v>Error: keys and values must have the same number of cells</v>
       </c>
     </row>
   </sheetData>
@@ -1178,13 +1190,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{570C164C-BACA-45EE-A434-9925DD3C362F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B555F199-EC81-457D-836F-A9521B159827}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1200,7 +1212,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B4" t="str">
         <f>RTD("redisrtd",,"GET","test.redisexcel.key","localhost:6379")</f>
@@ -1212,7 +1224,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B5" t="str">
         <f>RTD("redisrtd",,"HGET","test.redisexcel.hash","campo1","localhost:6379")</f>
@@ -1224,19 +1236,19 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" t="str">
         <f>RTD("redisrtd",,"HGETALL","test.redisexcel.hash","localhost:6379")</f>
         <v>{"campo1":"valor1"}</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B7" t="str">
         <f>RTD("redisrtd",,"SUB","test.redisexcel.rtd","localhost:6379")</f>
@@ -1245,7 +1257,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B8" t="str">
         <f>RTD("redisrtd",,"PSUB","test.redisexcel.rtd*","localhost:6379")</f>
@@ -1263,7 +1275,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10">
         <f ca="1">_xll.RedisRTDTopicCount()</f>
@@ -1272,7 +1284,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B11">
         <f ca="1">_xll.RedisRTDSubscriptionCount()</f>
@@ -1281,7 +1293,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B12">
         <f ca="1">_xll.RedisRTDChannelCount()</f>
@@ -1290,7 +1302,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">_xll.RedisRTDDefaultHost()</f>
@@ -1299,7 +1311,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
@@ -1308,7 +1320,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B15">
         <f ca="1">_xll.RedisRTDRedisUpdateInterval()</f>
@@ -1317,7 +1329,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" t="b">
         <f ca="1">_xll.RedisRTDRealTimeUpdates()</f>
@@ -1326,7 +1338,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B20" t="str">
         <f>RTD("redisrtd",,"GET")</f>
@@ -1335,14 +1347,14 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" t="str">
         <f>RTD("redisrtd",,"GET"," ","localhost:6379")</f>
         <v>ws_key_value</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{718E9C97-F3BD-48EA-9D2C-DBF4AC74E041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8D2F3AE-08A6-4969-929A-0944F299863E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{314ABDF6-4D98-4849-A9C5-078FB1684D1B}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{8971DE97-93A0-48AB-A3A1-2FEF3297C564}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -212,6 +212,15 @@
   </si>
   <si>
     <t>SetKV mismatched</t>
+  </si>
+  <si>
+    <t>PublishIfChanged</t>
+  </si>
+  <si>
+    <t>No change</t>
+  </si>
+  <si>
+    <t>Unsubscribe blank channel</t>
   </si>
   <si>
     <t>RedisExcel RTD tests (host localhost:6379)</t>
@@ -697,8 +706,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9872A662-9EB2-41B4-B0E1-22D68B3BC39D}">
-  <dimension ref="A1:H43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51F1B98-4C9B-41BD-99C1-A1F6F42668C7}">
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -917,7 +926,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.015000000000001</v>
+        <v>98.196999999999989</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -941,7 +950,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -950,7 +959,7 @@
       </c>
       <c r="B22">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1182,6 +1191,27 @@
       <c r="B43" t="str">
         <f ca="1">_xll.RedisUDFSetKV($F$2:$G$2,$F$3)</f>
         <v>Error: keys and values must have the same number of cells</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" t="str">
+        <f ca="1">_xll.RedisUDFChannelPublishIfChanged("test.redisexcel.rtd2","same","localhost:6379")</f>
+        <v>No change</v>
+      </c>
+      <c r="C44" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" t="str">
+        <f ca="1">_xll.RedisUDFChannelUnsubscribe("   ")</f>
+        <v>Error: a channel is required</v>
       </c>
     </row>
   </sheetData>
@@ -1190,13 +1220,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B555F199-EC81-457D-836F-A9521B159827}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45F33BF0-FFB0-41FB-A58D-35C41A220545}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1212,7 +1242,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B4" t="str">
         <f>RTD("redisrtd",,"GET","test.redisexcel.key","localhost:6379")</f>
@@ -1224,7 +1254,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B5" t="str">
         <f>RTD("redisrtd",,"HGET","test.redisexcel.hash","campo1","localhost:6379")</f>
@@ -1236,19 +1266,19 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B6" t="str">
         <f>RTD("redisrtd",,"HGETALL","test.redisexcel.hash","localhost:6379")</f>
         <v>{"campo1":"valor1"}</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B7" t="str">
         <f>RTD("redisrtd",,"SUB","test.redisexcel.rtd","localhost:6379")</f>
@@ -1257,7 +1287,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B8" t="str">
         <f>RTD("redisrtd",,"PSUB","test.redisexcel.rtd*","localhost:6379")</f>
@@ -1275,7 +1305,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B10">
         <f ca="1">_xll.RedisRTDTopicCount()</f>
@@ -1284,7 +1314,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B11">
         <f ca="1">_xll.RedisRTDSubscriptionCount()</f>
@@ -1293,7 +1323,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B12">
         <f ca="1">_xll.RedisRTDChannelCount()</f>
@@ -1302,7 +1332,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">_xll.RedisRTDDefaultHost()</f>
@@ -1311,7 +1341,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
@@ -1320,7 +1350,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B15">
         <f ca="1">_xll.RedisRTDRedisUpdateInterval()</f>
@@ -1329,7 +1359,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B16" t="b">
         <f ca="1">_xll.RedisRTDRealTimeUpdates()</f>
@@ -1338,7 +1368,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B20" t="str">
         <f>RTD("redisrtd",,"GET")</f>
@@ -1347,14 +1377,14 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B21" t="str">
         <f>RTD("redisrtd",,"GET"," ","localhost:6379")</f>
         <v>ws_key_value</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8D2F3AE-08A6-4969-929A-0944F299863E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B4EFD20-9E5E-464A-B939-5F663FD3B8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{8971DE97-93A0-48AB-A3A1-2FEF3297C564}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{850A31EE-C1CF-48F5-A90C-C80F2B0686A9}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="81">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -223,6 +223,12 @@
     <t>Unsubscribe blank channel</t>
   </si>
   <si>
+    <t>HashSetMultiple pairs</t>
+  </si>
+  <si>
+    <t>HashGet pairs</t>
+  </si>
+  <si>
     <t>RedisExcel RTD tests (host localhost:6379)</t>
   </si>
   <si>
@@ -272,6 +278,9 @@
   </si>
   <si>
     <t>ws_key_value</t>
+  </si>
+  <si>
+    <t>HGETALL missing hash</t>
   </si>
 </sst>
 </file>
@@ -348,6 +357,14 @@
         <tr r="B5" s="2"/>
       </tp>
       <tp t="s">
+        <v>{}</v>
+        <stp/>
+        <stp>HGETALL</stp>
+        <stp>test.redisexcel.missinghash</stp>
+        <stp>localhost:6379</stp>
+        <tr r="B22" s="2"/>
+      </tp>
+      <tp t="s">
         <v>#ERROR: ConnectData: GET requires a key as the second argument</v>
         <stp/>
         <stp>GET</stp>
@@ -370,7 +387,7 @@
         <tr r="B7" s="2"/>
       </tp>
       <tp t="s">
-        <v>hello_from_udf</v>
+        <v>hello_v2</v>
         <stp/>
         <stp>GET</stp>
         <stp>test.redisexcel.key</stp>
@@ -378,7 +395,7 @@
         <tr r="B4" s="2"/>
       </tp>
       <tp t="s">
-        <v>ws_key_value</v>
+        <v>(no value)</v>
         <stp/>
         <stp>GET</stp>
         <stp xml:space="preserve"> </stp>
@@ -706,8 +723,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51F1B98-4C9B-41BD-99C1-A1F6F42668C7}">
-  <dimension ref="A1:H45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C4C6ADD-984A-4084-8E24-C597D6F40A32}">
+  <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -761,7 +778,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">_xll.RedisUDFGet("test.redisexcel.key","localhost:6379")</f>
-        <v>hello_from_udf</v>
+        <v>hello_v2</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -926,7 +943,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.196999999999989</v>
+        <v>98.491</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -950,7 +967,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>129</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -959,7 +976,7 @@
       </c>
       <c r="B22">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1212,6 +1229,27 @@
       <c r="B45" t="str">
         <f ca="1">_xll.RedisUDFChannelUnsubscribe("   ")</f>
         <v>Error: a channel is required</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" t="str">
+        <f ca="1">_xll.RedisUDFHashSetMultiple("test.redisexcel.pairs",$F$2:$G$3,"localhost:6379")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47" t="str">
+        <f ca="1">_xll.RedisUDFHashGet("test.redisexcel.pairs","1","localhost:6379")</f>
+        <v>linha1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1220,13 +1258,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45F33BF0-FFB0-41FB-A58D-35C41A220545}">
-  <dimension ref="A1:C21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8B336C-6AFB-4024-AF07-FB26C8A403FC}">
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1242,11 +1280,11 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B4" t="str">
         <f>RTD("redisrtd",,"GET","test.redisexcel.key","localhost:6379")</f>
-        <v>hello_from_udf</v>
+        <v>hello_v2</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -1254,7 +1292,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B5" t="str">
         <f>RTD("redisrtd",,"HGET","test.redisexcel.hash","campo1","localhost:6379")</f>
@@ -1266,19 +1304,19 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" t="str">
         <f>RTD("redisrtd",,"HGETALL","test.redisexcel.hash","localhost:6379")</f>
         <v>{"campo1":"valor1"}</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B7" t="str">
         <f>RTD("redisrtd",,"SUB","test.redisexcel.rtd","localhost:6379")</f>
@@ -1287,7 +1325,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B8" t="str">
         <f>RTD("redisrtd",,"PSUB","test.redisexcel.rtd*","localhost:6379")</f>
@@ -1300,21 +1338,21 @@
       </c>
       <c r="B9">
         <f ca="1">_xll.RedisRTDConnectionCount()</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B10">
         <f ca="1">_xll.RedisRTDTopicCount()</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B11">
         <f ca="1">_xll.RedisRTDSubscriptionCount()</f>
@@ -1323,7 +1361,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B12">
         <f ca="1">_xll.RedisRTDChannelCount()</f>
@@ -1332,7 +1370,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">_xll.RedisRTDDefaultHost()</f>
@@ -1341,7 +1379,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
@@ -1350,7 +1388,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B15">
         <f ca="1">_xll.RedisRTDRedisUpdateInterval()</f>
@@ -1359,7 +1397,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B16" t="b">
         <f ca="1">_xll.RedisRTDRealTimeUpdates()</f>
@@ -1368,7 +1406,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B20" t="str">
         <f>RTD("redisrtd",,"GET")</f>
@@ -1377,14 +1415,23 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B21" t="str">
         <f>RTD("redisrtd",,"GET"," ","localhost:6379")</f>
-        <v>ws_key_value</v>
+        <v>(no value)</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="str">
+        <f>RTD("redisrtd",,"HGETALL","test.redisexcel.missinghash","localhost:6379")</f>
+        <v>{}</v>
       </c>
     </row>
   </sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B4EFD20-9E5E-464A-B939-5F663FD3B8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3DB787A-BCEF-480C-B331-4F59707A148A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{850A31EE-C1CF-48F5-A90C-C80F2B0686A9}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{E1482016-A736-4F64-B836-B1BB5E789429}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -723,7 +723,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C4C6ADD-984A-4084-8E24-C597D6F40A32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9859F707-378E-40EB-B1D7-FAB277FDDEE8}">
   <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -778,7 +778,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">_xll.RedisUDFGet("test.redisexcel.key","localhost:6379")</f>
-        <v>hello_v2</v>
+        <v>hello_from_udf</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.491</v>
+        <v>98.001999999999995</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>143</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -976,7 +976,7 @@
       </c>
       <c r="B22">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>140</v>
+        <v>437</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1258,7 +1258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E8B336C-6AFB-4024-AF07-FB26C8A403FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE498-E965-460B-A1EE-4BF0B2F32D36}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B9">
         <f ca="1">_xll.RedisRTDConnectionCount()</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3DB787A-BCEF-480C-B331-4F59707A148A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA4C3169-0C45-40AF-AC61-2C4CEC847B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{E1482016-A736-4F64-B836-B1BB5E789429}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{2DA2DB09-C080-4006-B58F-5BF1BAA66049}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="83">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -281,6 +281,12 @@
   </si>
   <si>
     <t>HGETALL missing hash</t>
+  </si>
+  <si>
+    <t>SetNonVolatile</t>
+  </si>
+  <si>
+    <t>IncrNonVolatile</t>
   </si>
 </sst>
 </file>
@@ -723,8 +729,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9859F707-378E-40EB-B1D7-FAB277FDDEE8}">
-  <dimension ref="A1:H47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB053C72-EB91-4742-8D74-6612A274FAB8}">
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -778,7 +784,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">_xll.RedisUDFGet("test.redisexcel.key","localhost:6379")</f>
-        <v>hello_from_udf</v>
+        <v>hello_v2</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -943,7 +949,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.001999999999995</v>
+        <v>98.546999999999997</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -967,7 +973,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>446</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -976,7 +982,7 @@
       </c>
       <c r="B22">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>437</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1250,6 +1256,24 @@
       </c>
       <c r="C47" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" t="str">
+        <f>_xll.RedisUDFSetNonVolatile("test.redisexcel.nvkey","v1","localhost:6379")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49">
+        <f>_xll.RedisUDFIncrNonVolatile("test.redisexcel.nvcounter","localhost:6379")</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE498-E965-460B-A1EE-4BF0B2F32D36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE65069-E721-431C-A289-74E6CD38CC70}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1383,7 +1407,7 @@
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA4C3169-0C45-40AF-AC61-2C4CEC847B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E20FEF76-C3D0-4640-9A4A-0275629EBED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{2DA2DB09-C080-4006-B58F-5BF1BAA66049}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{6FDCA6AA-6EFF-4BB1-B64B-400EC0A4D9BC}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -353,6 +353,58 @@
         <stp>localhost:6379</stp>
         <tr r="B6" s="2"/>
       </tp>
+    </main>
+    <main first="rtdsrv_43a5ede2991d42c0b8004436e2e2364b">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>682e6eb1-5329-4ed1-929b-5742b20c9f44</stp>
+        <tr r="B45" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_43a5ede2991d42c0b8004436e2e2364b">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>524252c7-c97d-4421-a1e4-bd1fa24a9f9e</stp>
+        <tr r="B31" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_43a5ede2991d42c0b8004436e2e2364b">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>9145b6e4-d0e6-4c1b-997f-ac25936d1c9b</stp>
+        <tr r="B21" s="1"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>c9156aca-36cc-40a2-8f2e-f25640b34c3b</stp>
+        <tr r="B10" s="1"/>
+      </tp>
+    </main>
+    <main first="rtdsrv_43a5ede2991d42c0b8004436e2e2364b">
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>f0ba7a59-f950-43cb-8584-31e280b7ddff</stp>
+        <tr r="B37" s="1"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>626cdfdd-9a18-4399-beef-997f0920f927</stp>
+        <tr r="B35" s="1"/>
+      </tp>
+      <tp>
+        <v>1</v>
+        <stp/>
+        <stp>7078a8ae-5da0-4240-bf50-804dd52fd064</stp>
+        <tr r="B43" s="1"/>
+      </tp>
+    </main>
+    <main first="redisrtd">
       <tp t="s">
         <v>valor1</v>
         <stp/>
@@ -370,6 +422,8 @@
         <stp>localhost:6379</stp>
         <tr r="B22" s="2"/>
       </tp>
+    </main>
+    <main first="redisrtd">
       <tp t="s">
         <v>#ERROR: ConnectData: GET requires a key as the second argument</v>
         <stp/>
@@ -729,7 +783,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB053C72-EB91-4742-8D74-6612A274FAB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B27F2B0-BB9E-40C4-81FF-A71251313A1F}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -772,7 +826,7 @@
       </c>
       <c r="B4" t="str">
         <f ca="1">_xll.RedisUDFSet("test.redisexcel.key","hello_from_udf","localhost:6379")</f>
-        <v>OK</v>
+        <v>OK FireForget</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -784,7 +838,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">_xll.RedisUDFGet("test.redisexcel.key","localhost:6379")</f>
-        <v>hello_v2</v>
+        <v>hello_from_udf</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -820,7 +874,7 @@
       </c>
       <c r="B8" t="str">
         <f ca="1">_xll.RedisUDFSetJSON("test.redisexcel.json",$F$2:$G$3,"localhost:6379")</f>
-        <v>OK</v>
+        <v>OK FireForget</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
@@ -842,9 +896,9 @@
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B10" t="e">
         <f ca="1">_xll.RedisUDFHashSet("test.redisexcel.hash","campo1","valor1","localhost:6379")</f>
-        <v>OK</v>
+        <v>#N/A</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
@@ -868,7 +922,7 @@
       </c>
       <c r="B12" t="str">
         <f ca="1">_xll.RedisUDFChannelPublish("test.redisexcel.channel","ola_mundo","localhost:6379")</f>
-        <v>1 readers(s)</v>
+        <v>OK FireForget</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -937,7 +991,7 @@
       </c>
       <c r="B18" t="str">
         <f ca="1">_xll.RedisUDFSetEx("test.redisexcel.tmp","x","100","localhost:6379")</f>
-        <v>OK</v>
+        <v>OK FireForget</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
@@ -949,7 +1003,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.546999999999997</v>
+        <v>99.673999999999992</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -971,18 +1025,18 @@
       <c r="A21" t="s">
         <v>27</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="e">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>150</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>28</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="str">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>147</v>
+        <v>OK FireForget</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1024,7 +1078,7 @@
       </c>
       <c r="B26" t="str">
         <f ca="1">_xll.RedisUDFSet("test.redisexcel.locale",$H$2,"localhost:6379")</f>
-        <v>OK</v>
+        <v>OK FireForget</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
@@ -1048,7 +1102,7 @@
       </c>
       <c r="B28" t="str">
         <f ca="1">_xll.RedisUDFSet($H$2,"dec-key","localhost:6379")</f>
-        <v>OK</v>
+        <v>OK FireForget</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
@@ -1082,9 +1136,9 @@
       <c r="A31" t="s">
         <v>40</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="e">
         <f ca="1">_xll.RedisUDFSetRemove("test.redisexcel.set","missing","localhost:6379")</f>
-        <v>0</v>
+        <v>#N/A</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1130,9 +1184,9 @@
       <c r="A35" t="s">
         <v>47</v>
       </c>
-      <c r="B35" t="str">
+      <c r="B35" t="e">
         <f ca="1">IF(_xll.RedisUDFListPopRight("test.redisexcel.emptylist","localhost:6379")="","empty","not empty")</f>
-        <v>empty</v>
+        <v>#N/A</v>
       </c>
       <c r="C35" t="s">
         <v>48</v>
@@ -1154,9 +1208,9 @@
       <c r="A37" t="s">
         <v>50</v>
       </c>
-      <c r="B37" t="str">
+      <c r="B37" t="e">
         <f ca="1">_xll.RedisUDFRename("test.redisexcel.missingrename","test.redisexcel.renamed","localhost:6379")</f>
-        <v>Error: ERR no such key</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1211,9 +1265,9 @@
       <c r="A43" t="s">
         <v>57</v>
       </c>
-      <c r="B43" t="str">
+      <c r="B43" t="e">
         <f ca="1">_xll.RedisUDFSetKV($F$2:$G$2,$F$3)</f>
-        <v>Error: keys and values must have the same number of cells</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1232,9 +1286,9 @@
       <c r="A45" t="s">
         <v>60</v>
       </c>
-      <c r="B45" t="str">
+      <c r="B45" t="e">
         <f ca="1">_xll.RedisUDFChannelUnsubscribe("   ")</f>
-        <v>Error: a channel is required</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1243,7 +1297,7 @@
       </c>
       <c r="B46" t="str">
         <f ca="1">_xll.RedisUDFHashSetMultiple("test.redisexcel.pairs",$F$2:$G$3,"localhost:6379")</f>
-        <v>OK</v>
+        <v>OK FireForget</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1264,7 +1318,7 @@
       </c>
       <c r="B48" t="str">
         <f>_xll.RedisUDFSetNonVolatile("test.redisexcel.nvkey","v1","localhost:6379")</f>
-        <v>OK</v>
+        <v>OK FireForget</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1282,7 +1336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE65069-E721-431C-A289-74E6CD38CC70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14363D7F-8E75-488A-BC13-5862E65F4280}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E20FEF76-C3D0-4640-9A4A-0275629EBED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE4D87DE-E00C-43BF-8DA5-FD9D00D3C01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{6FDCA6AA-6EFF-4BB1-B64B-400EC0A4D9BC}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{7980D18B-628C-406B-BD1A-AE9F243A1B8B}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -353,58 +353,6 @@
         <stp>localhost:6379</stp>
         <tr r="B6" s="2"/>
       </tp>
-    </main>
-    <main first="rtdsrv_43a5ede2991d42c0b8004436e2e2364b">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>682e6eb1-5329-4ed1-929b-5742b20c9f44</stp>
-        <tr r="B45" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_43a5ede2991d42c0b8004436e2e2364b">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>524252c7-c97d-4421-a1e4-bd1fa24a9f9e</stp>
-        <tr r="B31" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_43a5ede2991d42c0b8004436e2e2364b">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>9145b6e4-d0e6-4c1b-997f-ac25936d1c9b</stp>
-        <tr r="B21" s="1"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>c9156aca-36cc-40a2-8f2e-f25640b34c3b</stp>
-        <tr r="B10" s="1"/>
-      </tp>
-    </main>
-    <main first="rtdsrv_43a5ede2991d42c0b8004436e2e2364b">
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>f0ba7a59-f950-43cb-8584-31e280b7ddff</stp>
-        <tr r="B37" s="1"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>626cdfdd-9a18-4399-beef-997f0920f927</stp>
-        <tr r="B35" s="1"/>
-      </tp>
-      <tp>
-        <v>1</v>
-        <stp/>
-        <stp>7078a8ae-5da0-4240-bf50-804dd52fd064</stp>
-        <tr r="B43" s="1"/>
-      </tp>
-    </main>
-    <main first="redisrtd">
       <tp t="s">
         <v>valor1</v>
         <stp/>
@@ -422,8 +370,6 @@
         <stp>localhost:6379</stp>
         <tr r="B22" s="2"/>
       </tp>
-    </main>
-    <main first="redisrtd">
       <tp t="s">
         <v>#ERROR: ConnectData: GET requires a key as the second argument</v>
         <stp/>
@@ -783,7 +729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B27F2B0-BB9E-40C4-81FF-A71251313A1F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE5522A3-7F29-4A18-8DA6-35668502760C}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -838,7 +784,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">_xll.RedisUDFGet("test.redisexcel.key","localhost:6379")</f>
-        <v>hello_from_udf</v>
+        <v>hello_v2</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -896,9 +842,9 @@
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" t="e">
+      <c r="B10" t="str">
         <f ca="1">_xll.RedisUDFHashSet("test.redisexcel.hash","campo1","valor1","localhost:6379")</f>
-        <v>#N/A</v>
+        <v>OK FireForget</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
@@ -1003,7 +949,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>99.673999999999992</v>
+        <v>98.491</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1025,9 +971,9 @@
       <c r="A21" t="s">
         <v>27</v>
       </c>
-      <c r="B21" t="e">
+      <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>#N/A</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1136,9 +1082,9 @@
       <c r="A31" t="s">
         <v>40</v>
       </c>
-      <c r="B31" t="e">
+      <c r="B31">
         <f ca="1">_xll.RedisUDFSetRemove("test.redisexcel.set","missing","localhost:6379")</f>
-        <v>#N/A</v>
+        <v>0</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1184,9 +1130,9 @@
       <c r="A35" t="s">
         <v>47</v>
       </c>
-      <c r="B35" t="e">
+      <c r="B35" t="str">
         <f ca="1">IF(_xll.RedisUDFListPopRight("test.redisexcel.emptylist","localhost:6379")="","empty","not empty")</f>
-        <v>#N/A</v>
+        <v>empty</v>
       </c>
       <c r="C35" t="s">
         <v>48</v>
@@ -1208,9 +1154,9 @@
       <c r="A37" t="s">
         <v>50</v>
       </c>
-      <c r="B37" t="e">
+      <c r="B37" t="str">
         <f ca="1">_xll.RedisUDFRename("test.redisexcel.missingrename","test.redisexcel.renamed","localhost:6379")</f>
-        <v>#N/A</v>
+        <v>OK FireForget</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1265,9 +1211,9 @@
       <c r="A43" t="s">
         <v>57</v>
       </c>
-      <c r="B43" t="e">
+      <c r="B43" t="str">
         <f ca="1">_xll.RedisUDFSetKV($F$2:$G$2,$F$3)</f>
-        <v>#N/A</v>
+        <v>Error: keys and values must have the same number of cells</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1286,9 +1232,9 @@
       <c r="A45" t="s">
         <v>60</v>
       </c>
-      <c r="B45" t="e">
+      <c r="B45" t="str">
         <f ca="1">_xll.RedisUDFChannelUnsubscribe("   ")</f>
-        <v>#N/A</v>
+        <v>Error: a channel is required</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1336,7 +1282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14363D7F-8E75-488A-BC13-5862E65F4280}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD18C66-C32F-426B-A175-5C4EB4EFF649}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE4D87DE-E00C-43BF-8DA5-FD9D00D3C01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06317A0D-422D-4F7B-90B2-25A8F8D34DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{7980D18B-628C-406B-BD1A-AE9F243A1B8B}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{B1D6CC0A-F6C7-4A84-8A23-6AF5F662C6FD}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -729,7 +729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE5522A3-7F29-4A18-8DA6-35668502760C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C53123-EBFB-4F55-BE10-85061CB1AEEE}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -949,7 +949,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.491</v>
+        <v>98.48599999999999</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1282,7 +1282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD18C66-C32F-426B-A175-5C4EB4EFF649}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7727DED3-1AAF-4174-904A-E1F7B777A7AF}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06317A0D-422D-4F7B-90B2-25A8F8D34DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22D25D3D-56A9-4ED8-85A1-5CD035B9334C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{B1D6CC0A-F6C7-4A84-8A23-6AF5F662C6FD}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{318E66F4-B021-447F-9D21-561F4AAA64BA}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -729,7 +729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C53123-EBFB-4F55-BE10-85061CB1AEEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB17CF8E-AF58-4687-B1E1-6308567E3525}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -949,7 +949,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.48599999999999</v>
+        <v>98.492999999999995</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>240</v>
+        <v>374</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1282,7 +1282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7727DED3-1AAF-4174-904A-E1F7B777A7AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C91F0B-8443-4F44-8EB6-4F0A78F4A6E8}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22D25D3D-56A9-4ED8-85A1-5CD035B9334C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54874B63-2F50-4AD7-B8E6-0416BD3DEDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{318E66F4-B021-447F-9D21-561F4AAA64BA}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{4D1A2768-07A3-441F-88BB-F4FFF87D0DBF}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -729,7 +729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB17CF8E-AF58-4687-B1E1-6308567E3525}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF71F4D4-A98C-4BB4-84F0-12DCC73D7765}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -911,7 +911,7 @@
       <c r="A16" t="s">
         <v>23</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B16">
         <f ca="1">INDEX(_xll.RedisUDFTTLMultiples({"test.redisexcel.key"},"localhost:6379"),1,2)</f>
         <v>-1</v>
       </c>
@@ -949,7 +949,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.492999999999995</v>
+        <v>96.816999999999993</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="B21">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>374</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1282,7 +1282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10C91F0B-8443-4F44-8EB6-4F0A78F4A6E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7ED2D1B-F2D2-4DD7-A95D-3E474D714D7F}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54874B63-2F50-4AD7-B8E6-0416BD3DEDD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23164F3E-5F08-4447-BA01-7AF4E983589B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{4D1A2768-07A3-441F-88BB-F4FFF87D0DBF}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{E849E415-158E-4338-9A3C-02BBBAFB98FB}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -729,7 +729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF71F4D4-A98C-4BB4-84F0-12DCC73D7765}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD689C96-BC85-4E21-B81C-21AD42D772BE}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -949,7 +949,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>96.816999999999993</v>
+        <v>98.507999999999996</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -1282,7 +1282,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7ED2D1B-F2D2-4DD7-A95D-3E474D714D7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38098415-6AA4-472C-B1C4-B7E86F40DCFA}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/test/RedisExcel.Test.xlsx
+++ b/test/RedisExcel.Test.xlsx
@@ -6,9 +6,9 @@
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23164F3E-5F08-4447-BA01-7AF4E983589B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F81AE0FE-188B-47D1-AD87-A4FE40B876D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{E849E415-158E-4338-9A3C-02BBBAFB98FB}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{1B554EA8-6FB7-40C7-A689-1A251DE17F15}"/>
   </bookViews>
   <sheets>
     <sheet name="UDF" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="85">
   <si>
     <t>RedisExcel UDF tests (host localhost:6379, prefix test.redisexcel)</t>
   </si>
@@ -94,7 +94,7 @@
     <t>ChannelPublish</t>
   </si>
   <si>
-    <t>1 readers(s)</t>
+    <t>1 reader</t>
   </si>
   <si>
     <t>ChannelLatest</t>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>HashGet pairs</t>
+  </si>
+  <si>
+    <t>CheckConfigFile</t>
+  </si>
+  <si>
+    <t>JsonSchemaContents length</t>
   </si>
   <si>
     <t>RedisExcel RTD tests (host localhost:6379)</t>
@@ -414,7 +420,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -729,8 +735,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD689C96-BC85-4E21-B81C-21AD42D772BE}">
-  <dimension ref="A1:H49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEBB5BB5-4203-4FB2-A704-132E090E4B3B}">
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -772,7 +778,7 @@
       </c>
       <c r="B4" t="str">
         <f ca="1">_xll.RedisUDFSet("test.redisexcel.key","hello_from_udf","localhost:6379")</f>
-        <v>OK FireForget</v>
+        <v>OK (fire and forget)</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -820,7 +826,7 @@
       </c>
       <c r="B8" t="str">
         <f ca="1">_xll.RedisUDFSetJSON("test.redisexcel.json",$F$2:$G$3,"localhost:6379")</f>
-        <v>OK FireForget</v>
+        <v>OK (fire and forget)</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
@@ -844,7 +850,7 @@
       </c>
       <c r="B10" t="str">
         <f ca="1">_xll.RedisUDFHashSet("test.redisexcel.hash","campo1","valor1","localhost:6379")</f>
-        <v>OK FireForget</v>
+        <v>OK (fire and forget)</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
@@ -868,7 +874,7 @@
       </c>
       <c r="B12" t="str">
         <f ca="1">_xll.RedisUDFChannelPublish("test.redisexcel.channel","ola_mundo","localhost:6379")</f>
-        <v>OK FireForget</v>
+        <v>OK (fire and forget)</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -937,7 +943,7 @@
       </c>
       <c r="B18" t="str">
         <f ca="1">_xll.RedisUDFSetEx("test.redisexcel.tmp","x","100","localhost:6379")</f>
-        <v>OK FireForget</v>
+        <v>OK (fire and forget)</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
@@ -949,7 +955,7 @@
       </c>
       <c r="B19">
         <f ca="1">_xll.RedisUDFTTL("test.redisexcel.tmp","localhost:6379")</f>
-        <v>98.507999999999996</v>
+        <v>98.575999999999993</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -959,9 +965,9 @@
       <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="str">
         <f ca="1">_xll.RedisUDFDel("test.redisexcel.neverexists","localhost:6379")</f>
-        <v>0</v>
+        <v>OK (fire and forget: all)</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -971,9 +977,9 @@
       <c r="A21" t="s">
         <v>27</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="str">
         <f ca="1">_xll.RedisUDFIncr("test.redisexcel.counter","localhost:6379")</f>
-        <v>239</v>
+        <v>OK (fire and forget: all)</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -982,7 +988,7 @@
       </c>
       <c r="B22" t="str">
         <f ca="1">_xll.RedisUDFListPushRight("test.redisexcel.list","a","localhost:6379")</f>
-        <v>OK FireForget</v>
+        <v>OK (fire and forget)</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1001,9 +1007,9 @@
       <c r="A24" t="s">
         <v>31</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="str">
         <f ca="1">_xll.RedisUDFSetAdd("test.redisexcel.set","x","localhost:6379")</f>
-        <v>0</v>
+        <v>OK (fire and forget: all)</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -1024,7 +1030,7 @@
       </c>
       <c r="B26" t="str">
         <f ca="1">_xll.RedisUDFSet("test.redisexcel.locale",$H$2,"localhost:6379")</f>
-        <v>OK FireForget</v>
+        <v>OK (fire and forget)</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
@@ -1048,7 +1054,7 @@
       </c>
       <c r="B28" t="str">
         <f ca="1">_xll.RedisUDFSet($H$2,"dec-key","localhost:6379")</f>
-        <v>OK FireForget</v>
+        <v>OK (fire and forget)</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
@@ -1070,9 +1076,9 @@
       <c r="A30" t="s">
         <v>39</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="str">
         <f ca="1">_xll.RedisUDFHashDel("test.redisexcel.hash","missing","localhost:6379")</f>
-        <v>0</v>
+        <v>OK (fire and forget: all)</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1082,9 +1088,9 @@
       <c r="A31" t="s">
         <v>40</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="str">
         <f ca="1">_xll.RedisUDFSetRemove("test.redisexcel.set","missing","localhost:6379")</f>
-        <v>0</v>
+        <v>OK (fire and forget: all)</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1132,7 +1138,7 @@
       </c>
       <c r="B35" t="str">
         <f ca="1">IF(_xll.RedisUDFListPopRight("test.redisexcel.emptylist","localhost:6379")="","empty","not empty")</f>
-        <v>empty</v>
+        <v>not empty</v>
       </c>
       <c r="C35" t="s">
         <v>48</v>
@@ -1144,7 +1150,7 @@
       </c>
       <c r="B36" t="str">
         <f ca="1">IF(_xll.RedisUDFListPopLeft("test.redisexcel.emptylist","localhost:6379")="","empty","not empty")</f>
-        <v>empty</v>
+        <v>not empty</v>
       </c>
       <c r="C36" t="s">
         <v>48</v>
@@ -1156,7 +1162,7 @@
       </c>
       <c r="B37" t="str">
         <f ca="1">_xll.RedisUDFRename("test.redisexcel.missingrename","test.redisexcel.renamed","localhost:6379")</f>
-        <v>OK FireForget</v>
+        <v>OK (fire and forget)</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1243,7 +1249,7 @@
       </c>
       <c r="B46" t="str">
         <f ca="1">_xll.RedisUDFHashSetMultiple("test.redisexcel.pairs",$F$2:$G$3,"localhost:6379")</f>
-        <v>OK FireForget</v>
+        <v>OK (fire and forget)</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1260,20 +1266,38 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B48" t="str">
         <f>_xll.RedisUDFSetNonVolatile("test.redisexcel.nvkey","v1","localhost:6379")</f>
-        <v>OK FireForget</v>
+        <v>OK (fire and forget)</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>82</v>
-      </c>
-      <c r="B49">
+        <v>84</v>
+      </c>
+      <c r="B49" t="str">
         <f>_xll.RedisUDFIncrNonVolatile("test.redisexcel.nvcounter","localhost:6379")</f>
-        <v>1</v>
+        <v>OK (fire and forget: all)</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" t="str">
+        <f ca="1">_xll.RedisCheckConfigFile()</f>
+        <v>OK (C:\Users\rober\RedisExcel.json)</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56">
+        <f ca="1">LEN(_xll.RedisJsonSchemaContents())</f>
+        <v>4189</v>
       </c>
     </row>
   </sheetData>
@@ -1282,13 +1306,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38098415-6AA4-472C-B1C4-B7E86F40DCFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9562012E-06F5-42DF-9D9D-3BC23F20EB3A}">
   <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1304,7 +1328,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B4" t="str">
         <f>RTD("redisrtd",,"GET","test.redisexcel.key","localhost:6379")</f>
@@ -1316,7 +1340,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B5" t="str">
         <f>RTD("redisrtd",,"HGET","test.redisexcel.hash","campo1","localhost:6379")</f>
@@ -1328,19 +1352,19 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B6" t="str">
         <f>RTD("redisrtd",,"HGETALL","test.redisexcel.hash","localhost:6379")</f>
         <v>{"campo1":"valor1"}</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B7" t="str">
         <f>RTD("redisrtd",,"SUB","test.redisexcel.rtd","localhost:6379")</f>
@@ -1349,7 +1373,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B8" t="str">
         <f>RTD("redisrtd",,"PSUB","test.redisexcel.rtd*","localhost:6379")</f>
@@ -1367,7 +1391,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B10">
         <f ca="1">_xll.RedisRTDTopicCount()</f>
@@ -1376,7 +1400,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11">
         <f ca="1">_xll.RedisRTDSubscriptionCount()</f>
@@ -1385,7 +1409,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B12">
         <f ca="1">_xll.RedisRTDChannelCount()</f>
@@ -1394,16 +1418,16 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B13" t="str">
         <f ca="1">_xll.RedisRTDDefaultHost()</f>
-        <v>localhost:6379,password=,defaultDatabase=0,ssl=False,abortConnect=False</v>
+        <v>localhost:6379,password=****,defaultDatabase=0,ssl=False,abortConnect=False</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B14">
         <f ca="1">_xll.RedisRTDExcelUpdateInterval()</f>
@@ -1412,7 +1436,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B15">
         <f ca="1">_xll.RedisRTDRedisUpdateInterval()</f>
@@ -1421,7 +1445,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B16" t="b">
         <f ca="1">_xll.RedisRTDRealTimeUpdates()</f>
@@ -1430,7 +1454,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B20" t="str">
         <f>RTD("redisrtd",,"GET")</f>
@@ -1439,19 +1463,19 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B21" t="str">
         <f>RTD("redisrtd",,"GET"," ","localhost:6379")</f>
         <v>(no value)</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B22" t="str">
         <f>RTD("redisrtd",,"HGETALL","test.redisexcel.missinghash","localhost:6379")</f>
